--- a/docs/workbook-split/dateien/Bereinigungen.xlsx
+++ b/docs/workbook-split/dateien/Bereinigungen.xlsx
@@ -728,9 +728,8 @@
           <t>Gesamtleistung</t>
         </is>
       </c>
-      <c r="D7" s="6">
-        <f>SUM(E7:P7)</f>
-        <v/>
+      <c r="D7" s="6" t="n">
+        <v>24923</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>1920</v>
@@ -779,9 +778,8 @@
           <t>EBITDA vor verlustfreier Bewertung</t>
         </is>
       </c>
-      <c r="D8" s="6">
-        <f>SUM(E8:P8)</f>
-        <v/>
+      <c r="D8" s="6" t="n">
+        <v>950</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>292</v>
@@ -830,9 +828,8 @@
           <t>Verlustfreie Bewertung, gebucht</t>
         </is>
       </c>
-      <c r="D9" s="6">
-        <f>SUM(E9:P9)</f>
-        <v/>
+      <c r="D9" s="6" t="n">
+        <v>-447</v>
       </c>
       <c r="E9" s="6" t="n"/>
       <c r="F9" s="6" t="n"/>
@@ -865,9 +862,8 @@
           <t>Verlustfreie Bewertung, nicht gebucht</t>
         </is>
       </c>
-      <c r="D10" s="6">
-        <f>SUM(E10:P10)</f>
-        <v/>
+      <c r="D10" s="6" t="n">
+        <v>-293</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>0</v>
@@ -916,9 +912,8 @@
           <t>EBITDA (inkl. verlustfr. Bewertung)</t>
         </is>
       </c>
-      <c r="D11" s="6">
-        <f>SUM(E11:P11)</f>
-        <v/>
+      <c r="D11" s="6" t="n">
+        <v>210</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>292</v>
@@ -967,9 +962,8 @@
           <t>Rechtsberatung (SWM)</t>
         </is>
       </c>
-      <c r="D12" s="6">
-        <f>SUM(E12:P12)</f>
-        <v/>
+      <c r="D12" s="6" t="n">
+        <v>24</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>0</v>
@@ -1018,9 +1012,8 @@
           <t>Doppelbesetzung Overhead (2 GF, Buchhaltung)</t>
         </is>
       </c>
-      <c r="D13" s="6">
-        <f>SUM(E13:P13)</f>
-        <v/>
+      <c r="D13" s="6" t="n">
+        <v>334</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>0</v>
@@ -1069,9 +1062,8 @@
           <t>In 2025 beendete Projekte mit Vorratsbestand</t>
         </is>
       </c>
-      <c r="D14" s="6">
-        <f>SUM(E14:P14)</f>
-        <v/>
+      <c r="D14" s="6" t="n">
+        <v>-47</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>0</v>
@@ -1120,9 +1112,8 @@
           <t>Korrektur Aktivierung unfertige Erz. bis 12/2025</t>
         </is>
       </c>
-      <c r="D15" s="6">
-        <f>SUM(E15:P15)</f>
-        <v/>
+      <c r="D15" s="6" t="n">
+        <v>74</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>0</v>
@@ -1169,9 +1160,8 @@
           <t>B1 Brandenburg</t>
         </is>
       </c>
-      <c r="D16" s="6">
-        <f>SUM(E16:P16)</f>
-        <v/>
+      <c r="D16" s="6" t="n">
+        <v>63</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>0</v>
@@ -1220,9 +1210,8 @@
           <t>Parkallee Velten / Containerhalle KA</t>
         </is>
       </c>
-      <c r="D17" s="6">
-        <f>SUM(E17:P17)</f>
-        <v/>
+      <c r="D17" s="6" t="n">
+        <v>46</v>
       </c>
       <c r="E17" s="7" t="n">
         <v>0</v>
@@ -1271,9 +1260,8 @@
           <t>Korrektur Fehlbuchung 04/26</t>
         </is>
       </c>
-      <c r="D18" s="6">
-        <f>SUM(E18:P18)</f>
-        <v/>
+      <c r="D18" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>0</v>
@@ -1322,9 +1310,8 @@
           <t>Aktivierung unfertige Erzeugnisse (01/26)</t>
         </is>
       </c>
-      <c r="D19" s="6">
-        <f>SUM(E19:P19)</f>
-        <v/>
+      <c r="D19" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="E19" s="7" t="n">
         <v>-310</v>
@@ -1373,57 +1360,44 @@
           <t>EBITDA adjusted</t>
         </is>
       </c>
-      <c r="D20" s="9">
-        <f>SUM(E20:P20)</f>
-        <v/>
-      </c>
-      <c r="E20" s="9">
-        <f>E11+SUM(E12,E13,E14,E15,E16,E17,E18,E19)</f>
-        <v/>
-      </c>
-      <c r="F20" s="9">
-        <f>F11+SUM(F12,F13,F14,F15,F16,F17,F18,F19)</f>
-        <v/>
-      </c>
-      <c r="G20" s="9">
-        <f>G11+SUM(G12,G13,G14,G15,G16,G17,G18,G19)</f>
-        <v/>
-      </c>
-      <c r="H20" s="9">
-        <f>H11+SUM(H12,H13,H14,H15,H16,H17,H18,H19)</f>
-        <v/>
-      </c>
-      <c r="I20" s="9">
-        <f>I11+SUM(I12,I13,I14,I15,I16,I17,I18,I19)</f>
-        <v/>
-      </c>
-      <c r="J20" s="9">
-        <f>J11+SUM(J12,J13,J14,J15,J16,J17,J18,J19)</f>
-        <v/>
-      </c>
-      <c r="K20" s="9">
-        <f>K11+SUM(K12,K13,K14,K15,K16,K17,K18,K19)</f>
-        <v/>
-      </c>
-      <c r="L20" s="9">
-        <f>L11+SUM(L12,L13,L14,L15,L16,L17,L18,L19)</f>
-        <v/>
-      </c>
-      <c r="M20" s="9">
-        <f>M11+SUM(M12,M13,M14,M15,M16,M17,M18,M19)</f>
-        <v/>
-      </c>
-      <c r="N20" s="9">
-        <f>N11+SUM(N12,N13,N14,N15,N16,N17,N18,N19)</f>
-        <v/>
-      </c>
-      <c r="O20" s="9">
-        <f>O11+SUM(O12,O13,O14,O15,O16,O17,O18,O19)</f>
-        <v/>
-      </c>
-      <c r="P20" s="9">
-        <f>P11+SUM(P12,P13,P14,P15,P16,P17,P18,P19)</f>
-        <v/>
+      <c r="D20" s="9" t="n">
+        <v>704</v>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>-18</v>
+      </c>
+      <c r="F20" s="9" t="n">
+        <v>337</v>
+      </c>
+      <c r="G20" s="9" t="n">
+        <v>69</v>
+      </c>
+      <c r="H20" s="9" t="n">
+        <v>-92</v>
+      </c>
+      <c r="I20" s="9" t="n">
+        <v>-174</v>
+      </c>
+      <c r="J20" s="9" t="n">
+        <v>199</v>
+      </c>
+      <c r="K20" s="9" t="n">
+        <v>-83</v>
+      </c>
+      <c r="L20" s="9" t="n">
+        <v>-112</v>
+      </c>
+      <c r="M20" s="9" t="n">
+        <v>236</v>
+      </c>
+      <c r="N20" s="9" t="n">
+        <v>-125</v>
+      </c>
+      <c r="O20" s="9" t="n">
+        <v>92</v>
+      </c>
+      <c r="P20" s="9" t="n">
+        <v>375</v>
       </c>
       <c r="Q20" s="1" t="n"/>
       <c r="R20" s="1" t="n"/>
@@ -1436,9 +1410,8 @@
           <t>EBITDA-Marge adjusted</t>
         </is>
       </c>
-      <c r="D21" s="10">
-        <f>IF(D7=0,"n.a.",D20/D7)</f>
-        <v/>
+      <c r="D21" s="10" t="n">
+        <v>0.02824700076234803</v>
       </c>
       <c r="E21" s="10" t="n">
         <v>-0.008999999999999999</v>
@@ -2409,6 +2382,8 @@
       <c r="Q60" s="1" t="n"/>
       <c r="R60" s="1" t="n"/>
     </row>
+    <row r="61"/>
+    <row r="62"/>
     <row r="63">
       <c r="C63" t="inlineStr">
         <is>
